--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB28CA97-AE21-4839-A0BB-3A8E8A2F7853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD221F04-A7E6-4304-BE9A-B23B11767634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -181,7 +181,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;¥&quot;* #,##0.00_-\ ;\-&quot;¥&quot;* #,##0.00_-\ ;_-&quot;¥&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -281,7 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -296,16 +296,16 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1289,392 +1289,196 @@
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="4">
-        <v>45901</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="1">
-        <v>431294</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="4">
-        <v>45902</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" s="1">
-        <v>390600</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="4">
-        <v>45903</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="1">
-        <v>536697</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="4">
-        <v>45904</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" s="1">
-        <v>362512</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="4">
-        <v>45905</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" s="1">
-        <v>203502</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="4">
-        <v>45906</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" s="1">
-        <v>754771</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="4">
-        <v>45907</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C49" s="1">
-        <v>898941</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="4">
-        <v>45908</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="1">
-        <v>553112</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="4">
-        <v>45909</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C51" s="1">
-        <v>383247</v>
-      </c>
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="4">
-        <v>45910</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C52" s="1">
-        <v>399366</v>
-      </c>
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="4">
-        <v>45911</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="1">
-        <v>377619</v>
-      </c>
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="4">
-        <v>45912</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="1">
-        <v>427851</v>
-      </c>
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="4">
-        <v>45913</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C55" s="1">
-        <v>703128</v>
-      </c>
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="4">
-        <v>45914</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C56" s="1">
-        <v>688610</v>
-      </c>
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="4">
-        <v>45915</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C57" s="1">
-        <v>674175</v>
-      </c>
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="4">
-        <v>45916</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" s="1">
-        <v>329236</v>
-      </c>
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C59" s="6">
-        <v>487972</v>
-      </c>
+      <c r="A59" s="4"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="4">
-        <v>45918</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C60" s="6">
-        <v>351797</v>
-      </c>
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="6"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="4">
-        <v>45919</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C61" s="6">
-        <v>493571</v>
-      </c>
+      <c r="A61" s="4"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="6"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="4">
-        <v>45920</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C62" s="6">
-        <v>567140</v>
-      </c>
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="6"/>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="4">
-        <v>45921</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C63" s="6">
-        <v>691821</v>
-      </c>
+      <c r="A63" s="4"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="6"/>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="4">
-        <v>45922</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C64" s="6">
-        <v>495923</v>
-      </c>
+      <c r="A64" s="4"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6"/>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="4">
-        <v>45923</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C65" s="6">
-        <v>504131</v>
-      </c>
+      <c r="A65" s="4"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="6"/>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="4">
-        <v>45924</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C66" s="6">
-        <v>483672</v>
-      </c>
+      <c r="A66" s="4"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="6"/>
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A67" s="4">
-        <v>45925</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C67" s="6">
-        <v>333908</v>
-      </c>
+      <c r="A67" s="4"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="6"/>
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A68" s="4">
-        <v>45926</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C68" s="6">
-        <v>537605</v>
-      </c>
+      <c r="A68" s="4"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A69" s="4">
-        <v>45927</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" s="6">
-        <v>635011</v>
-      </c>
+      <c r="A69" s="4"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6"/>
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A70" s="4">
-        <v>45928</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C70" s="6">
-        <v>590174</v>
-      </c>
+      <c r="A70" s="4"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="6"/>
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A71" s="4">
-        <v>45929</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C71" s="6">
-        <v>554513</v>
-      </c>
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="6"/>
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A72" s="4">
-        <v>45930</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C72" s="6">
-        <v>729892</v>
-      </c>
+      <c r="A72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="6"/>
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,8 +208,32 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,13 +243,6 @@
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,23 +269,52 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,37 +328,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -320,32 +335,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,6 +346,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +410,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,37 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,11 +613,46 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,44 +674,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23043,8 +23043,19 @@
         <v>703799</v>
       </c>
     </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1723" s="2">
+        <v>625963</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,44 +208,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -260,8 +222,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,6 +271,45 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,37 +324,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,31 +353,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +392,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,19 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +488,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,97 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,36 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -624,6 +594,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,11 +627,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,11 +657,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23054,8 +23054,19 @@
         <v>625963</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1724" s="2">
+        <v>567745</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,8 +208,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,23 +219,22 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -249,15 +249,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -270,22 +285,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -294,7 +308,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,46 +330,25 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,7 +374,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,37 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,79 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,50 +603,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +645,188 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23065,8 +23065,19 @@
         <v>567745</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1725" s="2">
+        <v>496371</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,9 +208,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,7 +225,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,8 +244,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,6 +268,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -254,7 +285,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,37 +307,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,12 +323,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -321,31 +337,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -354,6 +347,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,6 +370,60 @@
       <patternFill patternType="solid">
         <fgColor indexed="54"/>
         <bgColor indexed="54"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -398,13 +452,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,109 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,15 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -607,6 +598,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -618,6 +618,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,43 +675,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23076,8 +23076,19 @@
         <v>496371</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1726" s="2">
+        <v>152812</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -215,6 +215,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -230,7 +268,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -244,33 +297,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,8 +312,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,16 +335,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,44 +356,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,19 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +410,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,145 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,30 +584,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -622,22 +598,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -676,6 +647,35 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -688,7 +688,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -697,7 +697,7 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -706,127 +706,127 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23087,8 +23087,19 @@
         <v>152812</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1727" s="2">
+        <v>591202</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -208,26 +208,18 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,52 +232,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -304,7 +253,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -312,24 +274,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -343,9 +290,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -356,6 +325,37 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,25 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,6 +416,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -440,7 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,85 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,6 +616,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -624,6 +636,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,24 +672,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -671,162 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23098,8 +23098,19 @@
         <v>591202</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1728" s="2">
+        <v>413137</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,67 +208,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,9 +238,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,31 +274,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -345,7 +323,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -356,6 +348,14 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +416,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,43 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,115 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,15 +579,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,21 +611,30 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -655,16 +655,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23109,8 +23109,19 @@
         <v>413137</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1729" s="2">
+        <v>409292</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -216,36 +216,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -261,6 +231,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -268,14 +284,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,25 +336,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,39 +353,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,73 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +410,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,37 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +482,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,8 +586,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,54 +612,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,6 +633,45 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23120,8 +23120,19 @@
         <v>409292</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1730" s="2">
+        <v>532046</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -211,6 +211,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -222,34 +237,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,9 +252,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,31 +267,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,14 +290,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -345,6 +314,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -352,8 +337,23 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,13 +374,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,139 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,13 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,17 +585,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -612,6 +605,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,23 +660,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,164 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23131,8 +23131,19 @@
         <v>532046</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1731" s="2">
+        <v>480369</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -211,20 +211,66 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,37 +285,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,23 +306,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,49 +352,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,19 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,43 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,25 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +428,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,31 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +518,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,11 +585,59 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,59 +657,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1731"/>
+  <dimension ref="A1:E1732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23142,8 +23142,19 @@
         <v>480369</v>
       </c>
     </row>
+    <row r="1732" spans="1:3">
+      <c r="A1732" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1732" s="2">
+        <v>917378</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1730">
+  <autoFilter ref="A1:E1731">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -209,16 +209,31 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -230,18 +245,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -253,17 +268,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -277,7 +284,61 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,70 +353,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,79 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,49 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +536,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,11 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,43 +607,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,6 +639,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -666,17 +657,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23153,8 +23153,19 @@
         <v>917378</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1733" s="2">
+        <v>347060</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -209,13 +209,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -229,11 +222,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,47 +296,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -306,21 +311,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -346,14 +345,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,73 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,19 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +464,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,25 +530,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,6 +584,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -602,48 +626,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,11 +655,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23164,8 +23164,19 @@
         <v>347060</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1734" s="2">
+        <v>346181</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -209,35 +209,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,25 +222,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -281,16 +250,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,17 +273,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,6 +290,21 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -344,10 +313,41 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,19 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +398,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,25 +446,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,31 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,19 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,31 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,6 +601,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -618,24 +627,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,6 +663,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -685,165 +685,165 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,9 +851,10 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1261,152 +1262,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="15"/>
+      <c r="A2" s="16"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="15"/>
+      <c r="A5" s="16"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="15"/>
+      <c r="A12" s="16"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="15"/>
+      <c r="A16" s="16"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="15"/>
+      <c r="A27" s="16"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1559,7 +1560,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23175,8 +23176,17 @@
         <v>346181</v>
       </c>
     </row>
+    <row r="1735" spans="1:3">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1735" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,7 +209,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,23 +245,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,7 +306,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,53 +337,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,26 +352,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,55 +470,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,49 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +587,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,17 +622,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,24 +672,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -665,168 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23197,8 +23197,19 @@
         <v>408055</v>
       </c>
     </row>
+    <row r="1737" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1737" s="2">
+        <v>407195</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -215,13 +215,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -231,46 +224,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,6 +244,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -299,14 +269,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,19 +298,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -346,7 +330,23 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,13 +374,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +434,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,31 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,73 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,25 +536,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,11 +622,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,17 +646,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,17 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,145 +688,145 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23208,8 +23208,19 @@
         <v>407195</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1738" s="2">
+        <v>569973</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -208,6 +208,14 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -216,15 +224,76 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,76 +314,16 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,17 +337,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,25 +374,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,43 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,19 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,37 +530,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,16 +593,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,26 +622,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23219,8 +23219,19 @@
         <v>569973</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1739" s="2">
+        <v>649019</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,6 +209,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -225,55 +233,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -299,6 +261,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -313,6 +305,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -321,24 +320,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -349,6 +341,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -380,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +404,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +452,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,85 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,10 +583,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -607,61 +633,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,57 +656,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -739,94 +718,115 @@
     <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23230,8 +23230,19 @@
         <v>649019</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1740" s="2">
+        <v>314423</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,16 +208,23 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -232,16 +239,22 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,38 +274,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,18 +288,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -336,26 +312,50 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +404,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +464,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,31 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -600,59 +624,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +656,177 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23241,8 +23241,19 @@
         <v>314423</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1741" s="2">
+        <v>255010</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,8 +208,31 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,29 +246,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -254,21 +262,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,16 +297,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -312,21 +329,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -335,15 +337,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -352,7 +352,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +386,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +428,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,145 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -598,11 +609,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,41 +635,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +662,171 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23252,8 +23252,19 @@
         <v>255010</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1742" s="2">
+        <v>444494</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,16 +208,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,9 +223,122 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,115 +353,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,151 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,32 +579,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,9 +615,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -666,8 +651,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +665,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23263,8 +23263,19 @@
         <v>444494</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1743" s="2">
+        <v>351030</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,47 +208,19 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -259,34 +231,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -305,19 +253,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -329,6 +275,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -337,8 +290,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -352,8 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,49 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,121 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,6 +609,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -624,11 +636,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,186 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23274,8 +23274,19 @@
         <v>351030</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1744" s="2">
+        <v>345485</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -210,22 +210,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,9 +239,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,59 +314,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,42 +335,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -380,7 +380,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +440,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,103 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,19 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,9 +585,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,6 +609,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -620,18 +652,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -651,32 +672,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,16 +688,16 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -706,127 +706,127 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23285,8 +23285,19 @@
         <v>345485</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1745" s="2">
+        <v>596705</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,7 +208,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -216,17 +215,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,7 +238,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,15 +246,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,6 +268,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -278,14 +305,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,47 +319,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -351,11 +335,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,13 +374,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,73 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,67 +524,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,11 +585,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,6 +631,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -641,33 +663,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,145 +688,145 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23296,8 +23296,19 @@
         <v>596705</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1746" s="2">
+        <v>616478</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,6 +208,7 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -216,15 +217,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,7 +231,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,8 +260,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,32 +285,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -311,30 +313,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -343,8 +321,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -374,43 +374,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +428,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,103 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,18 +585,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,21 +605,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,11 +641,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +671,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23307,8 +23307,19 @@
         <v>616478</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1747" s="2">
+        <v>505458</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,7 +208,67 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,13 +284,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -238,15 +291,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,24 +313,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,37 +343,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,22 +356,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +440,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,91 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,49 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -624,21 +624,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -666,8 +651,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,8 +660,23 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23318,8 +23318,19 @@
         <v>505458</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1748" s="2">
+        <v>505458</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,8 +208,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,7 +224,82 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,9 +313,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,105 +352,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -374,7 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +416,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,24 +512,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -518,13 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,25 +536,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,13 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,17 +613,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,6 +646,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -659,24 +672,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,16 +688,16 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -706,127 +706,127 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23329,8 +23329,19 @@
         <v>505458</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1749" s="2">
+        <v>289707</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,9 +208,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,8 +230,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,68 +253,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -314,7 +277,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,16 +336,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -345,17 +346,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,25 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +398,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +458,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,79 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,54 +618,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +641,192 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,9 +835,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
@@ -846,10 +846,10 @@
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23340,8 +23340,19 @@
         <v>289707</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1750" s="2">
+        <v>340795</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,7 +209,74 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,14 +291,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -239,7 +314,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,52 +335,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,49 +352,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,55 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,115 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,9 +585,41 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,17 +639,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,17 +653,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,21 +672,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23351,8 +23351,19 @@
         <v>340795</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1751" s="2">
+        <v>477830</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -209,28 +209,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -239,67 +217,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,24 +237,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,6 +319,45 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -374,7 +374,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,73 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,79 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -605,36 +594,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,6 +631,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -680,153 +654,179 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23362,8 +23362,19 @@
         <v>477830</v>
       </c>
     </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1752" s="2">
+        <v>379182</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -209,21 +209,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -231,7 +254,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,15 +314,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,43 +329,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -322,38 +353,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -380,7 +380,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +464,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,25 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,31 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,85 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,34 +598,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -646,11 +628,44 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -665,168 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23373,8 +23373,30 @@
         <v>379182</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1753" s="2">
+        <v>379182</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1754" s="2">
+        <v>688306</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -208,6 +208,42 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -216,9 +252,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,15 +275,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,44 +283,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,7 +298,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -307,36 +306,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -352,8 +329,31 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,49 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,85 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,69 +603,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +626,207 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23395,8 +23395,19 @@
         <v>688306</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1755" s="2">
+        <v>506244</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,11 +208,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,7 +238,70 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,62 +321,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,42 +337,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,25 +470,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,85 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,31 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,9 +585,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,26 +624,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -638,6 +635,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,17 +663,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23406,8 +23406,19 @@
         <v>506244</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1756" s="2">
+        <v>346201</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,22 +209,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -237,85 +237,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,11 +253,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,10 +283,79 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,49 +374,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,55 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +446,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +488,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,13 +583,74 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,74 +670,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23417,8 +23417,19 @@
         <v>346201</v>
       </c>
     </row>
+    <row r="1757" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1757" s="2">
+        <v>467931</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
@@ -208,22 +208,8 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -231,15 +217,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,7 +232,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,14 +277,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,29 +292,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -321,9 +321,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,6 +337,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -345,17 +352,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +386,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,37 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +458,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,31 +530,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,24 +612,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,6 +640,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -669,164 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23428,8 +23428,19 @@
         <v>467931</v>
       </c>
     </row>
+    <row r="1758" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1758" s="2">
+        <v>407022</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,16 +208,44 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,16 +259,70 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,36 +337,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,67 +356,6 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +434,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,85 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,6 +549,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,63 +579,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +623,210 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23439,8 +23439,19 @@
         <v>407022</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1759" s="2">
+        <v>382617</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,15 +208,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,14 +224,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,6 +260,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -259,9 +297,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,17 +313,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,22 +328,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -322,30 +338,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -353,7 +346,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -380,7 +380,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +422,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,42 +464,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -470,13 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,31 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,7 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -600,59 +635,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +665,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23450,8 +23450,19 @@
         <v>382617</v>
       </c>
     </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1760" s="2">
+        <v>399113</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,43 +208,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -253,83 +216,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -344,6 +231,119 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -353,7 +353,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,25 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +398,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,24 +470,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -464,19 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,49 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,56 +579,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -666,6 +616,47 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -680,153 +671,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23461,8 +23461,30 @@
         <v>399113</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1761" s="2">
+        <v>399113</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1762" s="2">
+        <v>531904</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,24 +208,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,45 +223,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,14 +238,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -305,16 +245,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,9 +267,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -352,8 +297,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,12 +370,6 @@
       <patternFill patternType="solid">
         <fgColor indexed="54"/>
         <bgColor indexed="54"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -398,6 +392,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -410,7 +422,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,25 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,109 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,35 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,17 +613,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,11 +657,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23483,8 +23483,19 @@
         <v>531904</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1763" s="2">
+        <v>564424</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,9 +208,16 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,7 +231,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,8 +252,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,6 +284,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -267,6 +312,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -274,57 +328,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -338,22 +346,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,61 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,79 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,6 +598,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -616,43 +640,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +669,164 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23494,8 +23494,19 @@
         <v>564424</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1764" s="2">
+        <v>139819</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,29 +209,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -244,11 +230,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,55 +252,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -328,11 +275,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,8 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,55 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,91 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,26 +598,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -665,7 +650,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,153 +665,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,9 +835,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
@@ -846,10 +846,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23505,8 +23505,19 @@
         <v>139819</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1765" s="2">
+        <v>451583</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,15 +209,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,15 +222,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,7 +275,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -267,37 +289,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,9 +313,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,33 +352,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,97 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,6 +410,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -494,19 +494,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,25 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -600,9 +609,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,6 +629,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,188 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -835,23 +835,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23516,8 +23516,19 @@
         <v>451583</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1766" s="2">
+        <v>282368</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -209,29 +209,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,22 +230,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,7 +246,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,15 +268,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,9 +290,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -313,9 +304,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,28 +358,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -374,31 +374,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,91 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,11 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,6 +624,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -629,21 +644,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,8 +660,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,148 +685,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23527,8 +23527,19 @@
         <v>282368</v>
       </c>
     </row>
+    <row r="1767" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1767" s="2">
+        <v>359988</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/矢切店.xlsx
+++ b/dashboard/data/incoming/矢切店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -208,10 +208,34 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -223,14 +247,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,7 +270,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -259,8 +298,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,9 +308,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -282,7 +330,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,29 +345,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -327,35 +352,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +386,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,121 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,11 +611,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -656,177 +680,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -836,14 +836,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1559,7 +1559,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23538,8 +23538,19 @@
         <v>359988</v>
       </c>
     </row>
+    <row r="1768" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1768" s="2">
+        <v>354984</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
